--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_r2/post_rank_positive_return/staggered_10_accounts_hold_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_r2/post_rank_positive_return/staggered_10_accounts_hold_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -471,7 +471,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.07683924831662747</v>
+        <v>-0.1660851642946688</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2973641828847431</v>
+        <v>0.1829779237854836</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.2054933295925565</v>
+        <v>-1.110728363144738</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.2808600725524142</v>
+        <v>-1.37293802095715</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2939714736490943</v>
+        <v>0.2292884806748389</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.2938650121362306</v>
+        <v>-0.8092462006212823</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>11.46006917349678</v>
+        <v>9.936401308214943</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2144127696897483</v>
+        <v>-0.17513122503525</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2323598980634462</v>
+        <v>0.2539016534825984</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.028763174523901</v>
+        <v>-0.7213607064099975</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.341679235086403</v>
+        <v>-0.981571677642525</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2696463011110236</v>
+        <v>0.2916590178315766</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8240712321692469</v>
+        <v>-0.6228770227447501</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>12.84907925948323</v>
+        <v>11.8573249499152</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.06450837509411389</v>
+        <v>-0.1210882815672358</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2244844609689033</v>
+        <v>0.2038405931582103</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.2639931285528376</v>
+        <v>-0.6304667091901774</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.3806797675712853</v>
+        <v>-0.8542779387616166</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2538158033143906</v>
+        <v>0.2478159695250803</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.264296283420263</v>
+        <v>-0.5074874034349832</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>12.49556348438901</v>
+        <v>12.49533478683864</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1028114876807307</v>
+        <v>0.03039176902536567</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2214886263732534</v>
+        <v>0.2679501660363449</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.5030337792032975</v>
+        <v>0.1938680784087734</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.7412955476040854</v>
+        <v>0.2800283299982623</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1638463647895809</v>
+        <v>0.1863479066785555</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.6547609192400097</v>
+        <v>0.1699364919158305</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>13.18840170811684</v>
+        <v>14.85598555681286</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3888822138429722</v>
+        <v>0.5469536179338961</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2678130790337877</v>
+        <v>0.3008621368573034</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.351917461436768</v>
+        <v>1.606675261650245</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.8924805737027</v>
+        <v>2.302936899752953</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1705904223225452</v>
+        <v>0.1866443555317707</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.37928631344572</v>
+        <v>3.065474881807592</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>14.12581831311684</v>
+        <v>12.14349915307587</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.08081564290811594</v>
+        <v>0.1358692380026214</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3626981979612235</v>
+        <v>0.3766328536800941</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.5280568418813488</v>
+        <v>0.7612512360635715</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.7578031173916941</v>
+        <v>1.086824571836314</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2445652405489765</v>
+        <v>0.1774242690760668</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.6186649354024272</v>
+        <v>1.464382955361858</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>11.84621795605996</v>
+        <v>11.95400417820859</v>
       </c>
     </row>
   </sheetData>
